--- a/data/trans_dic/P38C-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Habitat-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,67; 85,71</t>
+          <t>79,54; 85,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,26; 89,42</t>
+          <t>80,92; 89,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,25; 89,9</t>
+          <t>85,04; 90,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90,31; 94,13</t>
+          <t>90,42; 94,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,28; 87,32</t>
+          <t>83,38; 87,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,59; 91,16</t>
+          <t>86,95; 91,41</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,73; 84,85</t>
+          <t>79,81; 84,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,23; 78,92</t>
+          <t>30,3; 78,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,56; 92,01</t>
+          <t>88,36; 92,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,69; 87,02</t>
+          <t>82,64; 87,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,8; 87,89</t>
+          <t>85,01; 88,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,27; 82,04</t>
+          <t>49,05; 82,0</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,04; 83,14</t>
+          <t>76,92; 83,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,73; 82,89</t>
+          <t>74,33; 82,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,89; 89,53</t>
+          <t>84,45; 89,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,34; 94,46</t>
+          <t>85,45; 94,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,88; 85,8</t>
+          <t>81,89; 85,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,73; 90,41</t>
+          <t>81,75; 90,37</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,89; 82,94</t>
+          <t>77,51; 82,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,48; 82,95</t>
+          <t>76,25; 82,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,82; 86,46</t>
+          <t>82,13; 86,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,58; 87,06</t>
+          <t>64,4; 87,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,79; 84,17</t>
+          <t>80,84; 84,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,9; 84,0</t>
+          <t>70,97; 83,85</t>
         </is>
       </c>
     </row>
@@ -957,27 +957,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,23; 80,95</t>
+          <t>58,16; 81,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,35; 88,57</t>
+          <t>86,35; 88,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,73; 88,75</t>
+          <t>80,58; 88,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,65; 85,33</t>
+          <t>83,65; 85,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,67; 84,5</t>
+          <t>72,13; 84,41</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>533575; 574032</t>
+          <t>532702; 571150</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>516373; 568239</t>
+          <t>514172; 567919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>570335; 601440</t>
+          <t>568914; 602712</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>608924; 634692</t>
+          <t>609700; 635242</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1114887; 1169022</t>
+          <t>1116311; 1166220</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1134132; 1193895</t>
+          <t>1138756; 1197264</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>804819; 856515</t>
+          <t>805636; 855789</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>395932; 940249</t>
+          <t>361019; 940351</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>921073; 956901</t>
+          <t>918944; 957403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>789455; 830833</t>
+          <t>789028; 831543</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1737982; 1801329</t>
+          <t>1742232; 1804129</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1057391; 1760733</t>
+          <t>1052646; 1759807</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>577359; 623054</t>
+          <t>576437; 623404</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>526618; 584132</t>
+          <t>523767; 583458</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>663030; 699268</t>
+          <t>659612; 696833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>793999; 878888</t>
+          <t>795037; 879895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1253144; 1313151</t>
+          <t>1253237; 1313122</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1336365; 1478269</t>
+          <t>1336626; 1477628</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>723981; 770915</t>
+          <t>720428; 769611</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>708842; 768839</t>
+          <t>706690; 765877</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>848977; 897182</t>
+          <t>852283; 898764</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>717909; 953061</t>
+          <t>705055; 955421</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1589257; 1655752</t>
+          <t>1590285; 1655174</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1392962; 1698184</t>
+          <t>1434683; 1695070</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2689338; 2782281</t>
+          <t>2689455; 2781973</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1979099; 2799393</t>
+          <t>2011517; 2802762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3046246; 3124396</t>
+          <t>3046105; 3120388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2949914; 3243177</t>
+          <t>2944456; 3237367</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5759974; 5875968</t>
+          <t>5760286; 5881794</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5026322; 6009920</t>
+          <t>5130186; 6003651</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38C-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,54; 85,28</t>
+          <t>79,77; 85,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,92; 89,37</t>
+          <t>81,47; 88,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,04; 90,09</t>
+          <t>85,14; 90,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90,42; 94,21</t>
+          <t>89,35; 93,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,38; 87,11</t>
+          <t>83,34; 87,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,95; 91,41</t>
+          <t>86,38; 90,72</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,81; 84,78</t>
+          <t>79,77; 84,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,3; 78,93</t>
+          <t>73,54; 80,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,36; 92,06</t>
+          <t>88,57; 92,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,64; 87,1</t>
+          <t>82,35; 86,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,01; 88,03</t>
+          <t>84,81; 87,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,05; 82,0</t>
+          <t>78,87; 82,81</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,92; 83,19</t>
+          <t>77,13; 82,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,33; 82,8</t>
+          <t>73,93; 81,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,45; 89,21</t>
+          <t>84,89; 89,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,45; 94,57</t>
+          <t>83,11; 88,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,89; 85,8</t>
+          <t>81,73; 85,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,75; 90,37</t>
+          <t>79,53; 84,22</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,51; 82,8</t>
+          <t>77,85; 82,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,25; 82,63</t>
+          <t>75,22; 81,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,13; 86,61</t>
+          <t>81,82; 86,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64,4; 87,27</t>
+          <t>83,28; 87,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,84; 84,14</t>
+          <t>80,9; 84,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,97; 83,85</t>
+          <t>80,4; 84,24</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,09; 82,85</t>
+          <t>79,87; 82,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,16; 81,04</t>
+          <t>77,73; 81,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,35; 88,45</t>
+          <t>86,21; 88,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,58; 88,59</t>
+          <t>85,37; 87,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,65; 85,42</t>
+          <t>83,63; 85,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,13; 84,41</t>
+          <t>81,94; 84,0</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>546685</t>
+          <t>591380</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>623447</t>
+          <t>669938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1170132</t>
+          <t>1261318</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>532702; 571150</t>
+          <t>534240; 574060</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514172; 567919</t>
+          <t>562730; 613460</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>568914; 602712</t>
+          <t>569605; 603343</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>609700; 635242</t>
+          <t>653641; 682901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1116311; 1166220</t>
+          <t>1115715; 1167375</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1138756; 1197264</t>
+          <t>1228597; 1290252</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>737463</t>
+          <t>806672</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>811175</t>
+          <t>901423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1548638</t>
+          <t>1708095</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>805636; 855789</t>
+          <t>805242; 854019</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>361019; 940351</t>
+          <t>770376; 840626</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>918944; 957403</t>
+          <t>921129; 958344</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>789028; 831543</t>
+          <t>878278; 923898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1742232; 1804129</t>
+          <t>1738126; 1801625</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1052646; 1759807</t>
+          <t>1667372; 1750658</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>557432</t>
+          <t>626940</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>832381</t>
+          <t>693544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1389812</t>
+          <t>1320484</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>576437; 623404</t>
+          <t>578024; 621892</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>523767; 583458</t>
+          <t>593737; 657247</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>659612; 696833</t>
+          <t>663058; 698780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>795037; 879895</t>
+          <t>671311; 713370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1253237; 1313122</t>
+          <t>1250827; 1311919</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1336626; 1477628</t>
+          <t>1281046; 1356701</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>740676</t>
+          <t>777400</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886635</t>
+          <t>958045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1627311</t>
+          <t>1735445</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>720428; 769611</t>
+          <t>723580; 769015</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>706690; 765877</t>
+          <t>744729; 806034</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>852283; 898764</t>
+          <t>849015; 896947</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>705055; 955421</t>
+          <t>931251; 978679</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1590285; 1655174</t>
+          <t>1591371; 1655446</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1434683; 1695070</t>
+          <t>1695050; 1776018</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2582257</t>
+          <t>2802391</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3153638</t>
+          <t>3222951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5735894</t>
+          <t>6025342</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2689455; 2781973</t>
+          <t>2682118; 2780488</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2011517; 2802762</t>
+          <t>2744836; 2860933</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3046105; 3120388</t>
+          <t>3041339; 3123681</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2944456; 3237367</t>
+          <t>3179365; 3264943</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5760286; 5881794</t>
+          <t>5758371; 5881600</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5130186; 6003651</t>
+          <t>5945412; 6094685</t>
         </is>
       </c>
     </row>
